--- a/diseases/d126/2015-2019.xlsx
+++ b/diseases/d126/2015-2019.xlsx
@@ -44464,7 +44464,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -45543,7 +45543,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -46622,7 +46622,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -47701,7 +47701,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -48780,7 +48780,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -49859,7 +49859,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -50938,7 +50938,7 @@
       </c>
       <c r="AM310" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN310" t="b">
@@ -52017,7 +52017,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -54175,7 +54175,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -55254,7 +55254,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN334" t="b">
@@ -56333,7 +56333,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN340" t="b">
